--- a/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שרון יפעת - Fly</v>
+        <v>צוף מימון &amp; יקיר - שקוף</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410667&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410671&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-01</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שרון יפעת - Fly</v>
+        <v>צוף מימון &amp; יקיר - שקוף</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שירז - מאמי איפה עפת</v>
+        <v>אליאור נונה - מחרוזת עופר לוי 2026</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410666&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410670&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-01</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שירז - מאמי איפה עפת</v>
+        <v>אליאור נונה - מחרוזת עופר לוי 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>רות חתומה - תגיד לי &amp; Ya Ghayeb</v>
+        <v>אלשי שמואל - נכתב לנו מזמן</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410664&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410669&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-01</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>רות חתומה - תגיד לי &amp; Ya Ghayeb</v>
+        <v>אלשי שמואל - נכתב לנו מזמן</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עידו כנפי - לבכות על כתפך</v>
+        <v>איציק מארי - עוף מדבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410662&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410668&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-01</v>
@@ -583,202 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עידו כנפי - לבכות על כתפך</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>ישי סוויסה &amp; מיכאל סוויסה &amp; שחר חסון - מה הדיבור</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410661&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>ישי סוויסה &amp; מיכאל סוויסה &amp; שחר חסון - מה הדיבור</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>יהונתן שתיוי - גיב מי דאט</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410660&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>יהונתן שתיוי - גיב מי דאט</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>איציק מארי - כותב עלייך שיר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410659&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>איציק מארי - כותב עלייך שיר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אביחי פרץ - משבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410656&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אביחי פרץ - משבר</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>שרון הולצמן לראות אותך הלילה</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C10" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%a8%d7%95%d7%9f-%d7%94%d7%95%d7%9c%d7%a6%d7%9e%d7%9f-%d7%9c%d7%a8%d7%90%d7%95%d7%aa-%d7%90%d7%95%d7%aa%d7%9a-%d7%94%d7%9c%d7%99%d7%9c%d7%94/</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v>"לראות אותך הלילה" של שרון הולצמן הוא בלדת רוק אינטימית – כזו שלא נשענת על תחכום צורני אלא על רגש חשוף וישיר. דווקא הפשטות היא חלק מרכזי מהכוח שלה. כבר בשורה הפותחת נוצרת דינמיקה של תלות רגשית חזקה – "רק</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>שרון הולצמן לראות אותך הלילה</v>
+        <v>איציק מארי - עוף מדבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>צוף מימון &amp; יקיר - שקוף</v>
+        <v>אוליביה רודריגו Drop Dead</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410671&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%a8%d7%95%d7%93%d7%a8%d7%99%d7%92%d7%95-drop-dead/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>“לילה אחד השתעממתי במיטה / ועקבתי אחריך באינטרנט,” שרה אוליביה רודריגו בסינגל הקאמבק שלה, שכובש כל פסגה במצעדי העולם. שירים חדים, אובססיביים ובלתי מתפשרים על רומנטיקה – תמיד עם מודעות עצמית לעוצמה שלהם, או קריצה לאופן שבו בנות מאוהבות מתויגות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,126 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>צוף מימון &amp; יקיר - שקוף</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>אליאור נונה - מחרוזת עופר לוי 2026</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410670&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>אליאור נונה - מחרוזת עופר לוי 2026</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>אלשי שמואל - נכתב לנו מזמן</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410669&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>אלשי שמואל - נכתב לנו מזמן</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>איציק מארי - עוף מדבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410668&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>איציק מארי - עוף מדבר</v>
+        <v>אוליביה רודריגו Drop Dead</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אוליביה רודריגו Drop Dead</v>
+        <v>אריאל דימנט – כשאתה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%a8%d7%95%d7%93%d7%a8%d7%99%d7%92%d7%95-drop-dead/</v>
+        <v>https://yosmusic.com/%d7%90%d7%a8%d7%99%d7%90%d7%9c-%d7%93%d7%99%d7%9e%d7%a0%d7%98-%d7%9b%d7%a9%d7%90%d7%aa%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“לילה אחד השתעממתי במיטה / ועקבתי אחריך באינטרנט,” שרה אוליביה רודריגו בסינגל הקאמבק שלה, שכובש כל פסגה במצעדי העולם. שירים חדים, אובססיביים ובלתי מתפשרים על רומנטיקה – תמיד עם מודעות עצמית לעוצמה שלהם, או קריצה לאופן שבו בנות מאוהבות מתויגות</v>
+        <v>הקאבר ל־“כשאתה” בביצועה של אריאל דימנט מתוך המחזמר "בגלל הרוח" משירי שלומי שבת, הוא דוגמה יפה לאיך שיר אהבה מוכר יכול לקבל משמעות חדשה לגמרי כשהוא נכנס להקשר דרמטי. במקור, השיר של שלומי שבת בדואט עם בתו מנור שבת הוא</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אוליביה רודריגו Drop Dead</v>
+        <v>אריאל דימנט – כשאתה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>הפטריקים – מלאך</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%98%d7%a8%d7%99%d7%a7%d7%99%d7%9d-%d7%9e%d7%9c%d7%90%d7%9a/</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>“מלאך” של מאיר גולדברג ודודי לוי בביצוע  הפטריקים (דודי לוי + אבטיפוס) הוא טקסט טעון בדימויים פואטיים שמערבבים בין פנטזיה קוסמית לבין חוויה מאוד אנושית של אובדן, זיכרון וזהות. המלאך מתואר כיצור חופש שמביט מלמעלה, אך החופש הזה מתגלה כאשליה:</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>הפטריקים – מלאך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אריאל דימנט – כשאתה</v>
+        <v>שי אוחיון - צדיקה קטנה שלי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a8%d7%99%d7%90%d7%9c-%d7%93%d7%99%d7%9e%d7%a0%d7%98-%d7%9b%d7%a9%d7%90%d7%aa%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410688&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-03</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הקאבר ל־“כשאתה” בביצועה של אריאל דימנט מתוך המחזמר "בגלל הרוח" משירי שלומי שבת, הוא דוגמה יפה לאיך שיר אהבה מוכר יכול לקבל משמעות חדשה לגמרי כשהוא נכנס להקשר דרמטי. במקור, השיר של שלומי שבת בדואט עם בתו מנור שבת הוא</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אריאל דימנט – כשאתה</v>
+        <v>שי אוחיון - צדיקה קטנה שלי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>הפטריקים – מלאך</v>
+        <v>צוקוש - דוקטור</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-03</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%98%d7%a8%d7%99%d7%a7%d7%99%d7%9d-%d7%9e%d7%9c%d7%90%d7%9a/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410687&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-03</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>“מלאך” של מאיר גולדברג ודודי לוי בביצוע  הפטריקים (דודי לוי + אבטיפוס) הוא טקסט טעון בדימויים פואטיים שמערבבים בין פנטזיה קוסמית לבין חוויה מאוד אנושית של אובדן, זיכרון וזהות. המלאך מתואר כיצור חופש שמביט מלמעלה, אך החופש הזה מתגלה כאשליה:</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,12 +507,278 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>הפטריקים – מלאך</v>
+        <v>צוקוש - דוקטור</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>פנינה רוזנבלום - אני תוצרת ישראל</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410686&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>פנינה רוזנבלום - אני תוצרת ישראל</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>עמית אבני - הכחשה</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410685&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>עמית אבני - הכחשה</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ליטל - למה זה ככה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410684&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>ליטל - למה זה ככה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>יזהר כהן - ששון ושמחה</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410682&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>יזהר כהן - ששון ושמחה</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>טדי פופי - הכתר שלי</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410681&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>טדי פופי - הכתר שלי</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אנה זק - ילד שמנת</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410679&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אנה זק - ילד שמנת</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אחינועם - קיץ אחרון</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410678&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אחינועם - קיץ אחרון</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שי אוחיון - צדיקה קטנה שלי</v>
+        <v>יובל לוי – החיה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410688&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%9c%d7%95%d7%99-%d7%94%d7%97%d7%99%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>יובל לוי שרה שיר פופ שנשמע קליל וכיפי על יחסים בינה ובינו, אבל מתחת לפני השטח מסתתרת בו התפכחות לא פשוטה המציגה את הפער בין מה שדמיינת למה שהיה באמת הפתיחה: “אתה היית החיה שלי / הייתי היפה שלך” מייצרת</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,316 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שי אוחיון - צדיקה קטנה שלי</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>צוקוש - דוקטור</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410687&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>צוקוש - דוקטור</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>פנינה רוזנבלום - אני תוצרת ישראל</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410686&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>פנינה רוזנבלום - אני תוצרת ישראל</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>עמית אבני - הכחשה</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410685&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>עמית אבני - הכחשה</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>ליטל - למה זה ככה</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410684&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>ליטל - למה זה ככה</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>יזהר כהן - ששון ושמחה</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410682&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>יזהר כהן - ששון ושמחה</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>טדי פופי - הכתר שלי</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410681&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>טדי פופי - הכתר שלי</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אנה זק - ילד שמנת</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410679&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אנה זק - ילד שמנת</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אחינועם - קיץ אחרון</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410678&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אחינועם - קיץ אחרון</v>
+        <v>יובל לוי – החיה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל לוי – החיה</v>
+        <v>נינט – כחול לבן</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%9c%d7%95%d7%99-%d7%94%d7%97%d7%99%d7%94/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%99%d7%a0%d7%98-%d7%9b%d7%97%d7%95%d7%9c-%d7%9c%d7%91%d7%9f/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-04</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>יובל לוי שרה שיר פופ שנשמע קליל וכיפי על יחסים בינה ובינו, אבל מתחת לפני השטח מסתתרת בו התפכחות לא פשוטה המציגה את הפער בין מה שדמיינת למה שהיה באמת הפתיחה: “אתה היית החיה שלי / הייתי היפה שלך” מייצרת</v>
+        <v>השיר “כחול לבן” של נינט טייב הוא אחד השירים הפחות שגרתיים בפופ הישראלי – מין קולאז’ מוזיקלי שמערב הומור, נוסטלגיה, ביקורת תרבותית והצהרה אישית. זה שיר שלא מנסה להיות “יפה” במובן הקלאסי, אלא לשחק עם זהויות וסגנונות. הדבר הכי בולט</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל לוי – החיה</v>
+        <v>נינט – כחול לבן</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נינט – כחול לבן</v>
+        <v>קולות ברדא - צונה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%99%d7%a0%d7%98-%d7%9b%d7%97%d7%95%d7%9c-%d7%9c%d7%91%d7%9f/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410701&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-04</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “כחול לבן” של נינט טייב הוא אחד השירים הפחות שגרתיים בפופ הישראלי – מין קולאז’ מוזיקלי שמערב הומור, נוסטלגיה, ביקורת תרבותית והצהרה אישית. זה שיר שלא מנסה להיות “יפה” במובן הקלאסי, אלא לשחק עם זהויות וסגנונות. הדבר הכי בולט</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,468 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נינט – כחול לבן</v>
+        <v>קולות ברדא - צונה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>יואל אלהרר &amp; שמואל אלהרר - מול דרע</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410700&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>יואל אלהרר &amp; שמואל אלהרר - מול דרע</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>תעיזי &amp; רום לוף - ערסיתקלאסית</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410699&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>תעיזי &amp; רום לוף - ערסיתקלאסית</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>שמעון טובול · מחרוזת ל''ג בעומר 2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410698&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>שמעון טובול · מחרוזת ל''ג בעומר 2026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>שיראל חדד - קח את זה בקלות</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410697&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>שיראל חדד - קח את זה בקלות</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>שימי לנגא - הנשמה בוערת</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410696&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>שימי לנגא - הנשמה בוערת</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>עמרם בוסקילה &amp; מימון מני כהן - רבי מאיר ענני</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410695&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>עמרם בוסקילה &amp; מימון מני כהן - רבי מאיר ענני</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>נינט טייב - כחול לבן</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410694&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>נינט טייב - כחול לבן</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>יקיר יהודה יאיר - בר יוחאי</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410693&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>יקיר יהודה יאיר - בר יוחאי</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>יהודה שמעה - כה לחי</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410692&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>יהודה שמעה - כה לחי</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>דון יצחק מזרחי - מחרוזת רבי שמעון בר יוחאי 2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410691&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>דון יצחק מזרחי - מחרוזת רבי שמעון בר יוחאי 2026</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אוראל דוד - שלבי התבודדות</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410690&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אוראל דוד - שלבי התבודדות</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אבי אבורומי - קח אותי לתאילנד</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410689&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אבי אבורומי - קח אותי לתאילנד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קולות ברדא - צונה</v>
+        <v>מתנאל לוי - דרך חדשה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410701&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410710&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-04</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קולות ברדא - צונה</v>
+        <v>מתנאל לוי - דרך חדשה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יואל אלהרר &amp; שמואל אלהרר - מול דרע</v>
+        <v>קובי ברומר - בקודש הקדשים</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410700&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410709&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-04</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יואל אלהרר &amp; שמואל אלהרר - מול דרע</v>
+        <v>קובי ברומר - בקודש הקדשים</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>תעיזי &amp; רום לוף - ערסיתקלאסית</v>
+        <v>עומרי זליג - מחרוזת שאגת טדי 2026</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410699&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410708&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-04</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>תעיזי &amp; רום לוף - ערסיתקלאסית</v>
+        <v>עומרי זליג - מחרוזת שאגת טדי 2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שמעון טובול · מחרוזת ל''ג בעומר 2026</v>
+        <v>נריה אנג'ל - להיות רק בשמחה קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410698&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410707&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-04</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שמעון טובול · מחרוזת ל''ג בעומר 2026</v>
+        <v>נריה אנג'ל - להיות רק בשמחה קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>שיראל חדד - קח את זה בקלות</v>
+        <v>מורדי השורה מארחים את נוי דקל - טבעות העשן</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410697&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410705&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-04</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>שיראל חדד - קח את זה בקלות</v>
+        <v>מורדי השורה מארחים את נוי דקל - טבעות העשן</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>שימי לנגא - הנשמה בוערת</v>
+        <v>דרור אלוני - מחרוזת חפלה בך בוטח 2026</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410696&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410704&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-04</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>שימי לנגא - הנשמה בוערת</v>
+        <v>דרור אלוני - מחרוזת חפלה בך בוטח 2026</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>עמרם בוסקילה &amp; מימון מני כהן - רבי מאיר ענני</v>
+        <v>אליסף חפץ - ברכת מזל טוב</v>
       </c>
       <c r="B8" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410695&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410703&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-04</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>עמרם בוסקילה &amp; מימון מני כהן - רבי מאיר ענני</v>
+        <v>אליסף חפץ - ברכת מזל טוב</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>נינט טייב - כחול לבן</v>
+        <v>אביב צורף - רשב''י</v>
       </c>
       <c r="B9" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410694&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410702&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-04</v>
@@ -735,202 +735,12 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>נינט טייב - כחול לבן</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>יקיר יהודה יאיר - בר יוחאי</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410693&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>יקיר יהודה יאיר - בר יוחאי</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>יהודה שמעה - כה לחי</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410692&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>יהודה שמעה - כה לחי</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>דון יצחק מזרחי - מחרוזת רבי שמעון בר יוחאי 2026</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410691&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>דון יצחק מזרחי - מחרוזת רבי שמעון בר יוחאי 2026</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אוראל דוד - שלבי התבודדות</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410690&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אוראל דוד - שלבי התבודדות</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>אבי אבורומי - קח אותי לתאילנד</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410689&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>אבי אבורומי - קח אותי לתאילנד</v>
+        <v>אביב צורף - רשב''י</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מתנאל לוי - דרך חדשה</v>
+        <v>דנה ברגר – אם נותרנו נאהב</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410710&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
+        <v>https://yosmusic.com/%d7%93%d7%a0%d7%94-%d7%91%d7%a8%d7%92%d7%a8-%d7%90%d7%9d-%d7%a0%d7%95%d7%aa%d7%a8%d7%a0%d7%95-%d7%a0%d7%90%d7%94%d7%91/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>דנה ברגר שרה אמירה כמעט אידיאולוגית  מבלי להכביד. המסר: חיים עד הסוף, כאן ועכשיו למרות הכל  הטקסט יכול להתפרש גם כברירת מחדל, אבל בכיוון חיובי יותר הוא בנוי סביב בחירות – אם כבר עושים משהו – אז עד הסוף, אם</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מתנאל לוי - דרך חדשה</v>
+        <v>דנה ברגר – אם נותרנו נאהב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>קובי ברומר - בקודש הקדשים</v>
+        <v>אבי אבורומי – קח אותי לתאילנד</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410709&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%99-%d7%90%d7%91%d7%95%d7%a8%d7%95%d7%9e%d7%99-%d7%a7%d7%97-%d7%90%d7%95%d7%aa%d7%99-%d7%9c%d7%aa%d7%90%d7%99%d7%9c%d7%a0%d7%93/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>להיט  שנבנה קודם כל כדי לעבוד מהר לתפוס באז בהאזנה ראשונה, להיכנס לפלייליסטים, ולייצר תחושת בריחה מיידית. בבסיס השיר עומד רעיון מאוד ברור: עייפות מהשגרה רצון להתנתק מדרמות, מלחמות ולחצים, לממש פנטזיה של חופש מוחלט במקום אקזוטי (תאילנד) תאילנד כאן</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,240 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>קובי ברומר - בקודש הקדשים</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>עומרי זליג - מחרוזת שאגת טדי 2026</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410708&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>עומרי זליג - מחרוזת שאגת טדי 2026</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>נריה אנג'ל - להיות רק בשמחה קאבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410707&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>נריה אנג'ל - להיות רק בשמחה קאבר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>מורדי השורה מארחים את נוי דקל - טבעות העשן</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410705&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>מורדי השורה מארחים את נוי דקל - טבעות העשן</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>דרור אלוני - מחרוזת חפלה בך בוטח 2026</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410704&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>דרור אלוני - מחרוזת חפלה בך בוטח 2026</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אליסף חפץ - ברכת מזל טוב</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410703&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אליסף חפץ - ברכת מזל טוב</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אביב צורף - רשב''י</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410702&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אביב צורף - רשב''י</v>
+        <v>אבי אבורומי – קח אותי לתאילנד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דנה ברגר – אם נותרנו נאהב</v>
+        <v>תהילה זיאמר - פלסטר על הלב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-05</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a0%d7%94-%d7%91%d7%a8%d7%92%d7%a8-%d7%90%d7%9d-%d7%a0%d7%95%d7%aa%d7%a8%d7%a0%d7%95-%d7%a0%d7%90%d7%94%d7%91/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410735&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-05</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>דנה ברגר שרה אמירה כמעט אידיאולוגית  מבלי להכביד. המסר: חיים עד הסוף, כאן ועכשיו למרות הכל  הטקסט יכול להתפרש גם כברירת מחדל, אבל בכיוון חיובי יותר הוא בנוי סביב בחירות – אם כבר עושים משהו – אז עד הסוף, אם</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דנה ברגר – אם נותרנו נאהב</v>
+        <v>תהילה זיאמר - פלסטר על הלב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אבי אבורומי – קח אותי לתאילנד</v>
+        <v>רוחמה בן יוסף - יש סיכוי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-05</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%99-%d7%90%d7%91%d7%95%d7%a8%d7%95%d7%9e%d7%99-%d7%a7%d7%97-%d7%90%d7%95%d7%aa%d7%99-%d7%9c%d7%aa%d7%90%d7%99%d7%9c%d7%a0%d7%93/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410734&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-05</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>להיט  שנבנה קודם כל כדי לעבוד מהר לתפוס באז בהאזנה ראשונה, להיכנס לפלייליסטים, ולייצר תחושת בריחה מיידית. בבסיס השיר עומד רעיון מאוד ברור: עייפות מהשגרה רצון להתנתק מדרמות, מלחמות ולחצים, לממש פנטזיה של חופש מוחלט במקום אקזוטי (תאילנד) תאילנד כאן</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,12 +507,810 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אבי אבורומי – קח אותי לתאילנד</v>
+        <v>רוחמה בן יוסף - יש סיכוי</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נתנאל אבקסיס - נקודות של אור</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410733&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נתנאל אבקסיס - נקודות של אור</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>נריה קרמר - ניגונים</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410732&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>נריה קרמר - ניגונים</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מתן חסן - לא מפחד</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410731&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מתן חסן - לא מפחד</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>טלי רבקה סימן טוב - לוקחת רגע</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410730&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>טלי רבקה סימן טוב - לוקחת רגע</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>דניאל ברזילאי &amp; הדר הלל - הדבש הזה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410729&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>דניאל ברזילאי &amp; הדר הלל - הדבש הזה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>איתי לוי - פרח קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410728&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>איתי לוי - פרח קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אורן כדורי - פאן פאן פאן</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410727&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אורן כדורי - פאן פאן פאן</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אדל חן - שיר חדש</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410726&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אדל חן - שיר חדש</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אבינועם כהן - פותח דף חדש</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410725&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אבינועם כהן - פותח דף חדש</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>נעמי בניון - להיות בן אדם</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410724&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>נעמי בניון - להיות בן אדם</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>יגל אושרי - תגידי לי כן</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410723&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>יגל אושרי - תגידי לי כן</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>ששון שאולוב - נווה הדרים</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410722&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>ששון שאולוב - נווה הדרים</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>שרית חדד - המזרח הרחוק</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410721&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>שרית חדד - המזרח הרחוק</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>עידו מלכה - טפטופים</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410720&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>עידו מלכה - טפטופים</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>ינאי חיים לוי - פינה שקטה</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410719&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>ינאי חיים לוי - פינה שקטה</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>דנה ברגר - אם נותרנו נאהב</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410718&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>דנה ברגר - אם נותרנו נאהב</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>דיקלה - חולה מאהבה</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410717&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>דיקלה - חולה מאהבה</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>גיל ויין &amp; נופיה - להרגיש אישה</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C21" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410716&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>גיל ויין &amp; נופיה - להרגיש אישה</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>בר ניר - נרקיסיסט</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C22" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410715&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>בר ניר - נרקיסיסט</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>אסף הרץ - תופס אותו</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C23" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410714&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>אסף הרץ - תופס אותו</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>אור כהן - מגיע לי</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C24" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410713&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>אור כהן - מגיע לי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L24"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דה לאון - נופל וקם</v>
+        <v>שרית חדד – המזרח הרחוק</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410737&amp;sid=26b28b5b14677093a961099e7541cc4f</v>
+        <v>https://yosmusic.com/%d7%a9%d7%a8%d7%99%d7%aa-%d7%97%d7%93%d7%93-%d7%94%d7%9e%d7%96%d7%a8%d7%97-%d7%94%d7%a8%d7%97%d7%95%d7%a7/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>“המזרח הרחוק” ששרה שרית חדד הוא  פופ ים־תיכוני מלודי, זורם, נעים לאוזן  בקצב מיד-טמפו, מלודיה קליטה שמתפתחת בצורה חלקה, הפקה נקייה, כמעט “רדיו-פרנדלי” מושלמת.  שיר שנשמע כאילו נועד לנסיעה ארוכה, רדיו ברקע, האזנה כיפית. השורה “כמעט כל רמזור בעיר הפך</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דה לאון - נופל וקם</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>אברהם איילאו - הכל בעצמך</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-05</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410736&amp;sid=26b28b5b14677093a961099e7541cc4f</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-05</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>אברהם איילאו - הכל בעצמך</v>
+        <v>שרית חדד – המזרח הרחוק</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שרית חדד – המזרח הרחוק</v>
+        <v>גיל ויין &amp; נופיה – להרגיש אישה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%a8%d7%99%d7%aa-%d7%97%d7%93%d7%93-%d7%94%d7%9e%d7%96%d7%a8%d7%97-%d7%94%d7%a8%d7%97%d7%95%d7%a7/</v>
+        <v>https://yosmusic.com/%d7%92%d7%99%d7%9c-%d7%95%d7%99%d7%99%d7%9f-%d7%a0%d7%95%d7%a4%d7%99%d7%94-%d7%9c%d7%94%d7%a8%d7%92%d7%99%d7%a9-%d7%90%d7%99%d7%a9%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-06</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“המזרח הרחוק” ששרה שרית חדד הוא  פופ ים־תיכוני מלודי, זורם, נעים לאוזן  בקצב מיד-טמפו, מלודיה קליטה שמתפתחת בצורה חלקה, הפקה נקייה, כמעט “רדיו-פרנדלי” מושלמת.  שיר שנשמע כאילו נועד לנסיעה ארוכה, רדיו ברקע, האזנה כיפית. השורה “כמעט כל רמזור בעיר הפך</v>
+        <v>השיר “להרגיש אישה” ששרה נופיה הוא בלדה דרמטית שמנסה לתפוס רגע רגשי מאוד ספציפי – קשר קצר, עוצמתי, כמעט משקם,  ואז את ההתפרקות שלו. השיר נוגע בחוויה של אהבה לא יציבה, מהירה, ושברירית. השיר בנוי כמו סיפור כרונולוגי: מפגש אקראי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שרית חדד – המזרח הרחוק</v>
+        <v>גיל ויין &amp; נופיה – להרגיש אישה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>גיל ויין &amp; נופיה – להרגיש אישה</v>
+        <v>רון בי - להקת קיי פופ</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%99%d7%9c-%d7%95%d7%99%d7%99%d7%9f-%d7%a0%d7%95%d7%a4%d7%99%d7%94-%d7%9c%d7%94%d7%a8%d7%92%d7%99%d7%a9-%d7%90%d7%99%d7%a9%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410749&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-06</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “להרגיש אישה” ששרה נופיה הוא בלדה דרמטית שמנסה לתפוס רגע רגשי מאוד ספציפי – קשר קצר, עוצמתי, כמעט משקם,  ואז את ההתפרקות שלו. השיר נוגע בחוויה של אהבה לא יציבה, מהירה, ושברירית. השיר בנוי כמו סיפור כרונולוגי: מפגש אקראי</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,430 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>גיל ויין &amp; נופיה – להרגיש אישה</v>
+        <v>רון בי - להקת קיי פופ</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>רינת בר - אחת מאושרת</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410748&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>רינת בר - אחת מאושרת</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>רועי עומר - לא תדע (אהבה של אבא)</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410747&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>רועי עומר - לא תדע (אהבה של אבא)</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>רון בי - להקת בנים</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410746&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>רון בי - להקת בנים</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>עומרי אביב - לאן את הולכת</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410745&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>עומרי אביב - לאן את הולכת</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>מושיק עפיה - אין לי</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410744&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>מושיק עפיה - אין לי</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>דור הררי - גיבור על מדבקה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410743&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>דור הררי - גיבור על מדבקה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אלישבע - קפוא</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410742&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אלישבע - קפוא</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>איתן דרי - רכבת פרברים</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410741&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>איתן דרי - רכבת פרברים</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אילאי גואריהן - שריטות</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410740&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אילאי גואריהן - שריטות</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אור קודאי - פירורים</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410739&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אור קודאי - פירורים</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אבנר טואג - ככה תקבלו אותי</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410738&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אבנר טואג - ככה תקבלו אותי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רון בי - להקת קיי פופ</v>
+        <v>דיקלה – חולה מאהבה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410749&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%a7%d7%9c%d7%94-%d7%97%d7%95%d7%9c%d7%94-%d7%9e%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>דיקלה שרה בלדת פופ־מזרחית שמצליחה להפוך כאב זוגי מוכר למשהו כמעט פיזי. זה שיר שנשען פחות על תחכום ויותר על רגש חשוף. המילים “יש לי דירה ואין לי בית” הן המפתח לשיר. זו שורה פשוטה יחסית, אבל מאוד אפקטיבית: יש</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,430 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רון בי - להקת קיי פופ</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>רינת בר - אחת מאושרת</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410748&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>רינת בר - אחת מאושרת</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>רועי עומר - לא תדע (אהבה של אבא)</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410747&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>רועי עומר - לא תדע (אהבה של אבא)</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>רון בי - להקת בנים</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410746&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>רון בי - להקת בנים</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>עומרי אביב - לאן את הולכת</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410745&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>עומרי אביב - לאן את הולכת</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>מושיק עפיה - אין לי</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410744&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>מושיק עפיה - אין לי</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>דור הררי - גיבור על מדבקה</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410743&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>דור הררי - גיבור על מדבקה</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אלישבע - קפוא</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410742&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אלישבע - קפוא</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>איתן דרי - רכבת פרברים</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410741&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>איתן דרי - רכבת פרברים</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אילאי גואריהן - שריטות</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410740&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אילאי גואריהן - שריטות</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אור קודאי - פירורים</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410739&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אור קודאי - פירורים</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אבנר טואג - ככה תקבלו אותי</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410738&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אבנר טואג - ככה תקבלו אותי</v>
+        <v>דיקלה – חולה מאהבה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דיקלה – חולה מאהבה</v>
+        <v>משה זאודה - מחרוזת 1 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%a7%d7%9c%d7%94-%d7%97%d7%95%d7%9c%d7%94-%d7%9e%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410762&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-07</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>דיקלה שרה בלדת פופ־מזרחית שמצליחה להפוך כאב זוגי מוכר למשהו כמעט פיזי. זה שיר שנשען פחות על תחכום ויותר על רגש חשוף. המילים “יש לי דירה ואין לי בית” הן המפתח לשיר. זו שורה פשוטה יחסית, אבל מאוד אפקטיבית: יש</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,468 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דיקלה – חולה מאהבה</v>
+        <v>משה זאודה - מחרוזת 1 2026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ליאב מורחי - שלי לעולמים</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410761&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>ליאב מורחי - שלי לעולמים</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>מתן לוי - ילדה אחת</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410760&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>מתן לוי - ילדה אחת</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ליאב מורחי - קרוב אלייך</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410759&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>ליאב מורחי - קרוב אלייך</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>יניב סלמן - כמו אוויר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410758&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>יניב סלמן - כמו אוויר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>יהונתן מזרחי - בכל רגע תודה</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410757&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>יהונתן מזרחי - בכל רגע תודה</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>חן ביטון - ה' אוהב אותך</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410756&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>חן ביטון - ה' אוהב אותך</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>חיים דדון - שובי אליי</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410755&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>חיים דדון - שובי אליי</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>בן חן - נפלו לי השמיים</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410754&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>בן חן - נפלו לי השמיים</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אליהו חזן &amp; אשר חזן - מחרוזת שירי שבת 2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410753&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אליהו חזן &amp; אשר חזן - מחרוזת שירי שבת 2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אליאור זנדני - עיניים עצובות</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410752&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אליאור זנדני - עיניים עצובות</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אלי פרץ - מקנא בעצמי</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410751&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אלי פרץ - מקנא בעצמי</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אברהם אזן - זו התחלה</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410750&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אברהם אזן - זו התחלה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>